--- a/stick-world/config/excel/科技树.xlsx
+++ b/stick-world/config/excel/科技树.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="techs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="科技" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,11 +545,7 @@
           <t>economy</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>100</v>
       </c>
@@ -578,11 +574,7 @@
           <t>military</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>120</v>
       </c>
@@ -611,11 +603,7 @@
           <t>administration</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="n">
         <v>80</v>
       </c>
